--- a/research/mebs-competitors/MEBS_Competitors_UAE_Cleaning.xlsx
+++ b/research/mebs-competitors/MEBS_Competitors_UAE_Cleaning.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded (gov-linked)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cleaning Only'!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cleaning Only'!$A$1:$S$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MEBS Facility Services: 20 private-sector competitors (UAE)</t>
+          <t>MEBS Facility Services: 60 private-sector competitors (UAE), 20 per category</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1. FM Companies (8)  2. Security Only (6)  3. Cleaning Only (6)  4. MEBS benchmark  5. Excluded (gov-linked)
+          <t>1. FM Companies (20)  2. Security Only (20)  3. Cleaning Only (20)  4. MEBS benchmark  5. Excluded (gov-linked)
 Separate files are also provided per category.</t>
         </is>
       </c>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1267,8 +1267,1338 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Cleanpro Facilities Management Services LLC</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Cleaning and facility services</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi (branch in Garhoud, Dubai)</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Branches in Abu Dhabi and Dubai</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>Cleaning-led competitor in Abu Dhabi and Dubai</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>mefma.org (Cleanpro FMS); yellowpages-uae.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>WECARE Building Cleaning</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Building cleaning</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>WECARE business group. Owner not published</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>1,000+ (Dubai Govt HR listing)</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Nationwide workforce</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 45M to 65M</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Established Dubai building-cleaning contractor</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>Low to medium</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>waffer.dhr.gov.ae (WECARE Bldg Cleaning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Safaeewala Cleaning &amp; Technical Services LLC</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Deep cleaning, AC maintenance, technical services</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Family-run private company. Owner not published</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Private family</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Al Qusais, Dubai</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>50 to 249 (Clutch)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Residential and commercial deep cleaning</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 2M to 16M</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>Residential and commercial</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>Dubai cleaning competitor</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>clutch.co (Safaeewala); trustpilot.com; leadstal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>EcoClean</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Eco-friendly residential and commercial cleaning, AC and kitchen deep cleaning</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Not reliably published</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>201 to 500 (single profile, unverified)</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Heavy online marketing</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Residential, holiday homes, offices</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Visible Dubai cleaning brand</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>cyprus-mail.com; arabtimesonline.com (promotional coverage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Helpsters Cleaning Services LLC</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Maid service, deep cleaning, disinfection, commercial cleaning</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Burj Khalifa area, Dubai</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Home and commercial</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>Residential and commercial</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>Dubai cleaning competitor</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>propertyfinder.ae (cleaning companies); magicpin.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Urban Company UAE</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>App-based home cleaning (monthly subscriptions, 30-minute instant cleaning) and other home services</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Urban Company Limited (India)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Indian (parent)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Private (VC-backed, IPO-bound parent)</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Dubai 2018; Abu Dhabi 2019</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Dubai, Abu Dhabi, Sharjah</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Not published for UAE</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Also sold through the noon app</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Not published for UAE</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>Residential consumers</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>Residential cleaning platform</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>urbancompany.com (Abu Dhabi launch); khaleejtimes.com (monthly subscription); gulfnews.com (noon partnership)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Molly Maid Dubai</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Home and office cleaning</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Local franchisee (not published) of Molly Maid / Neighborly (USA)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Private franchise</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Approx. 25 years in Dubai (self-reported)</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>International franchise brand</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>Residential and offices</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>Branded home-cleaning competitor</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>business.google.com (Molly Maid Dubai); franchising.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>The Perfect Help (TPH Group)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Professional cleaning and maintenance</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Emirati-owned and managed. Owner not published</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Emirati</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Business Bay, Dubai</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Cleaning plus AC maintenance</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>Emirati-owned Dubai cleaning competitor</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>naukrigulf.com (TPH Group); ae.indeed.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Schon Building Cleaning Services LLC</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Commercial cleaning, deep cleaning, sanitisation</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>11 to 50 (directory)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Small commercial cleaner</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 0M to 3M</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>Dubai commercial cleaning competitor</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>ensun.io (commercial cleaning UAE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>CleaningCompany.ae</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Residential and commercial cleaning</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Featured by Gulf News as a start-up to watch</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>Residential and commercial</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>Dubai cleaning competitor</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>gulfnews.com ('A start-up to look out for in Dubai'); sothebysrealty.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Bookaclean</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Residential and commercial cleaning with flexible booking</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Ploesteanca Dumitrascu (per company press release, unverified)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Online booking</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>Residential and commercial</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>Dubai cleaning competitor</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>markets.financialcontent.com (ACCESS Newswire release); eyeofriyadh.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Helpbit Homes</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Home and office cleaning, pest control, moving, at-home salon</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Multi-service home platform</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>Residential and offices</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>Residential cleaning competitor</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>mustakbil.com (Helpbit Homes); squareyards.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Hello Cleaner</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Home and office cleaning</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>92 salary reviews on Indeed</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>Residential and offices</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>Dubai cleaning competitor</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>ae.indeed.com (Hello Cleaner); crunchbase.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Home Maids</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Hourly maid and home cleaning services</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Hourly maid supply</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>Residential cleaning competitor</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>khaleejtimes.com ('Home maids in Dubai')</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1417,7 +2747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1616,6 +2946,138 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Khadamat Facilities Management</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Set up as a JV of Mubadala (Abu Dhabi state investor) and Serco</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Ontegra (formerly Deyaar FM)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Subsidiary of Deyaar Development (government-linked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Tafawuq Facility Management</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Owned by Eltizam, which is 50% ADQ (Abu Dhabi state holding) and 50% IHC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Emirates International Facility Management</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Subsidiary of Das Holding, reported to be owned by Sheikh Mansour bin Zayed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Operon Middle East</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Owned by Edgenta, part of UEM Group, which belongs to Malaysia's state fund Khazanah</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Spark Security Services</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Acquired by Aldar Properties in 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>World Security</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Owned by DP World (Dubai Government)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>GardaWorld UAE</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Operates in the UAE through a joint venture with Transguard</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Global Security Services Group (GSSG)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Describes itself as the armed security provider for the UAE government</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Duserve FM &amp; Building Cleaning</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Owned by Dubai World Central (Government of Dubai)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Hitches &amp; Glitches</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Not separate: a subsidiary of Farnek, which is already listed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
